--- a/src/nand2tetris_implementation/machine_code_template.xlsx
+++ b/src/nand2tetris_implementation/machine_code_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinic\Documents\SPC\Engineering Club Cl Campus\Titan Processing Unit\Titan-Processing-Unit-TPU\src\nand2tetris_implementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF09ADBE-1488-47F4-B12D-7702F7B4DF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681ADB8A-96D0-4B77-AE12-3F3AAC052148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{0DBFB1C9-9435-4760-B78E-218CC4782F03}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0DBFB1C9-9435-4760-B78E-218CC4782F03}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>c</t>
   </si>
@@ -1256,10 +1256,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="17">
         <v>0</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="R12" t="str">
         <f t="shared" si="0"/>
-        <v>8C08</v>
+        <v>EC08</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="18" x14ac:dyDescent="0.3">
@@ -1651,47 +1651,114 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="18" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
+      <c r="A19" s="15">
+        <v>0</v>
+      </c>
+      <c r="B19" s="16">
+        <v>0</v>
+      </c>
+      <c r="C19" s="16">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0</v>
+      </c>
+      <c r="E19" s="18">
+        <v>0</v>
+      </c>
+      <c r="F19" s="18">
+        <v>0</v>
+      </c>
+      <c r="G19" s="18">
+        <v>0</v>
+      </c>
+      <c r="H19" s="18">
+        <v>0</v>
+      </c>
+      <c r="I19" s="18">
+        <v>0</v>
+      </c>
+      <c r="J19" s="18">
+        <v>0</v>
+      </c>
+      <c r="K19" s="19">
+        <v>0</v>
+      </c>
+      <c r="L19" s="19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="19">
+        <v>0</v>
+      </c>
+      <c r="N19" s="20">
+        <v>1</v>
+      </c>
+      <c r="O19" s="20">
+        <v>0</v>
+      </c>
+      <c r="P19" s="20">
+        <v>0</v>
+      </c>
       <c r="R19" t="str">
         <f t="shared" si="0"/>
-        <v>0000</v>
+        <v>0004</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="18" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
+      <c r="A20" s="15">
+        <v>1</v>
+      </c>
+      <c r="B20" s="16">
+        <v>1</v>
+      </c>
+      <c r="C20" s="16">
+        <v>1</v>
+      </c>
+      <c r="D20" s="17">
+        <v>0</v>
+      </c>
+      <c r="E20" s="18">
+        <v>1</v>
+      </c>
+      <c r="F20" s="18">
+        <v>1</v>
+      </c>
+      <c r="G20" s="18">
+        <v>0</v>
+      </c>
+      <c r="H20" s="18">
+        <v>0</v>
+      </c>
+      <c r="I20" s="18">
+        <v>0</v>
+      </c>
+      <c r="J20" s="18">
+        <v>0</v>
+      </c>
+      <c r="K20" s="19">
+        <v>0</v>
+      </c>
+      <c r="L20" s="19">
+        <v>0</v>
+      </c>
+      <c r="M20" s="19">
+        <v>1</v>
+      </c>
+      <c r="N20" s="20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="20">
+        <v>0</v>
+      </c>
+      <c r="P20" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>21</v>
+      </c>
       <c r="R20" t="str">
         <f t="shared" si="0"/>
-        <v>0000</v>
+        <v>EC08</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="18" x14ac:dyDescent="0.3">
